--- a/output/pdf_financials_xlsx/MIR.xlsx
+++ b/output/pdf_financials_xlsx/MIR.xlsx
@@ -4547,28 +4547,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>7.207647</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>8.202394</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>9.96677</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>9.96677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.305928</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.726487</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.031961</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -12638,7 +12638,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>7.207647</v>
       </c>
@@ -13748,7 +13752,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MIR.xlsx
+++ b/output/pdf_financials_xlsx/MIR.xlsx
@@ -2005,40 +2005,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.162458</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.262392</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.04612</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.155915</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.088897</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.401861</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.033461</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.013178</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.097595</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.01491</v>
       </c>
     </row>
     <row r="35">
@@ -2091,40 +2091,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.162458</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.262392</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.04612</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.155915</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.088897</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.401861</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.033461</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.013178</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.097595</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.01491</v>
       </c>
     </row>
     <row r="37">
@@ -2607,40 +2607,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.403728</v>
+        <v>0.24127</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.450019</v>
+        <v>0.187627</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.19859</v>
+        <v>0.15247</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.293919</v>
+        <v>0.138004</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.04153</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.100399</v>
+        <v>0.011502</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.480707</v>
+        <v>0.078846</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.089925</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.206373</v>
+        <v>0.172912</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.248598</v>
+        <v>0.23542</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.16723</v>
+        <v>0.069635</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.07495499999999999</v>
+        <v>0.060045</v>
       </c>
     </row>
     <row r="49">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/MIR.xlsx
+++ b/output/pdf_financials_xlsx/MIR.xlsx
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.169188</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.29736</v>
       </c>
       <c r="M70" s="3" t="n">
         <v>0</v>
@@ -3647,10 +3647,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.169188</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.29736</v>
       </c>
       <c r="M71" s="3" t="n">
         <v>0</v>
@@ -3819,10 +3819,10 @@
         <v>10.791443</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>11.713618</v>
+        <v>11.54443</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17.595926</v>
+        <v>17.298566</v>
       </c>
       <c r="M75" s="3" t="n">
         <v>18.463611</v>
@@ -4051,15 +4051,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K80" s="3" t="n">
+        <v>-0.0112554472544773</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>-0.01648647292547572</v>
       </c>
       <c r="M80" s="1" t="inlineStr">
         <is>
@@ -5285,19 +5281,19 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.524766</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.475994</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.5652740000000001</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.083009</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -8854,7 +8850,11 @@
           <t>Lease liabilities 10</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -20370,7 +20370,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E194" s="5" t="n">
         <v>0.524766</v>
       </c>
